--- a/data/trans_orig/P04B3_2_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P04B3_2_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si percibe la temperatura en la vivienda durante el invierno como un problema en 2023</t>
+          <t>Población según si percibe la temperatura en la vivienda durante el invierno como un problema en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>105787</t>
+          <t>104966</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>141003</t>
+          <t>141108</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>172540</t>
+          <t>170567</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>210171</t>
+          <t>211929</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>287360</t>
+          <t>289101</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>339800</t>
+          <t>339695</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70117</t>
+          <t>69532</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>99501</t>
+          <t>98297</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>115778</t>
+          <t>114344</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>147263</t>
+          <t>147731</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>193175</t>
+          <t>191303</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>236522</t>
+          <t>237482</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,69%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>70831</t>
+          <t>70883</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>102918</t>
+          <t>103174</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>127138</t>
+          <t>128869</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>160537</t>
+          <t>161703</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>206897</t>
+          <t>206808</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>251946</t>
+          <t>250595</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,72%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>202802</t>
+          <t>200875</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>243677</t>
+          <t>244817</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>270427</t>
+          <t>268683</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>310234</t>
+          <t>310149</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>484423</t>
+          <t>484436</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>542498</t>
+          <t>543759</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,8%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>270576</t>
+          <t>264422</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>448057</t>
+          <t>449381</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>325792</t>
+          <t>332370</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>610970</t>
+          <t>629344</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>673012</t>
+          <t>666963</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>997544</t>
+          <t>986387</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,79%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>177659</t>
+          <t>187588</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>315878</t>
+          <t>319189</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>185559</t>
+          <t>199108</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>301287</t>
+          <t>301714</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>423491</t>
+          <t>423858</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>601093</t>
+          <t>604092</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>299584</t>
+          <t>275663</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>488322</t>
+          <t>481838</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>244514</t>
+          <t>254917</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>400086</t>
+          <t>397400</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>625297</t>
+          <t>603181</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>856457</t>
+          <t>864072</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1071890</t>
+          <t>1067462</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1552266</t>
+          <t>1561188</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1060208</t>
+          <t>1062640</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1476953</t>
+          <t>1456666</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2183312</t>
+          <t>2193190</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2838753</t>
+          <t>2853389</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>63,03%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>67337</t>
+          <t>67859</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>101271</t>
+          <t>103571</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>61247</t>
+          <t>61319</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>90128</t>
+          <t>88448</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>135896</t>
+          <t>136292</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>180880</t>
+          <t>180696</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>67029</t>
+          <t>68264</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>104719</t>
+          <t>104313</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>60162</t>
+          <t>60185</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>88323</t>
+          <t>89615</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>136996</t>
+          <t>136923</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>184744</t>
+          <t>183298</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>104967</t>
+          <t>103271</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>146792</t>
+          <t>145527</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>105493</t>
+          <t>108351</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>141479</t>
+          <t>143583</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>220533</t>
+          <t>222463</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>276676</t>
+          <t>273942</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,99%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>325878</t>
+          <t>325461</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>382244</t>
+          <t>379462</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>365168</t>
+          <t>365462</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>411861</t>
+          <t>409176</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>703787</t>
+          <t>708452</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>776423</t>
+          <t>776237</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,47%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>466383</t>
+          <t>466434</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>655358</t>
+          <t>657473</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>592037</t>
+          <t>590986</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>917611</t>
+          <t>882774</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1141584</t>
+          <t>1122463</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1475294</t>
+          <t>1449945</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>342098</t>
+          <t>332907</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>495983</t>
+          <t>490598</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>379835</t>
+          <t>375118</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>513749</t>
+          <t>513508</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>789548</t>
+          <t>787075</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>985160</t>
+          <t>979897</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>487666</t>
+          <t>486781</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>696608</t>
+          <t>699091</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>495540</t>
+          <t>504842</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>671767</t>
+          <t>672589</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1067698</t>
+          <t>1068726</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1342959</t>
+          <t>1337960</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,84%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1643775</t>
+          <t>1651031</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2141853</t>
+          <t>2204417</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1727610</t>
+          <t>1734225</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2180369</t>
+          <t>2236738</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3445666</t>
+          <t>3449168</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4141195</t>
+          <t>4129734</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>58,15%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04B3_2_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P04B3_2_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>122671</t>
+          <t>138320</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>104966</t>
+          <t>119694</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>141108</t>
+          <t>157709</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>190595</t>
+          <t>214959</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>170567</t>
+          <t>196695</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>211929</t>
+          <t>233452</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>313266</t>
+          <t>353279</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>289101</t>
+          <t>326501</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>339695</t>
+          <t>385023</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>27,49%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>83247</t>
+          <t>92126</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69532</t>
+          <t>77369</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98297</t>
+          <t>110600</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>130343</t>
+          <t>140886</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>114344</t>
+          <t>124536</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>147731</t>
+          <t>154692</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>213590</t>
+          <t>233012</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>191303</t>
+          <t>211048</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>237482</t>
+          <t>257507</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>85471</t>
+          <t>102803</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>70883</t>
+          <t>86991</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>103174</t>
+          <t>120778</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>143719</t>
+          <t>154701</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>128869</t>
+          <t>138572</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>161703</t>
+          <t>173914</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>229190</t>
+          <t>257504</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>206808</t>
+          <t>234710</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>250595</t>
+          <t>285963</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>223550</t>
+          <t>245280</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>200875</t>
+          <t>221902</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>244817</t>
+          <t>271246</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>290851</t>
+          <t>311492</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>268683</t>
+          <t>291026</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>310149</t>
+          <t>333468</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>514401</t>
+          <t>556772</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>484436</t>
+          <t>524858</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>543759</t>
+          <t>591810</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,26%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>385843</t>
+          <t>455796</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>264422</t>
+          <t>419510</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>449381</t>
+          <t>503962</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>430251</t>
+          <t>426036</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>332370</t>
+          <t>393172</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>629344</t>
+          <t>460999</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>816095</t>
+          <t>881832</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>666963</t>
+          <t>824132</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>986387</t>
+          <t>937370</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,3%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>270184</t>
+          <t>300273</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>187588</t>
+          <t>267336</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>319189</t>
+          <t>340389</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>260737</t>
+          <t>299428</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>199108</t>
+          <t>270834</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>301714</t>
+          <t>330617</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>530921</t>
+          <t>599701</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>423858</t>
+          <t>550124</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>604092</t>
+          <t>643888</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>14,63%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>417392</t>
+          <t>439888</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>275663</t>
+          <t>392776</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>481838</t>
+          <t>484797</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>344924</t>
+          <t>396523</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>254917</t>
+          <t>365265</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>397400</t>
+          <t>433557</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>762315</t>
+          <t>836411</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>603181</t>
+          <t>785615</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>864072</t>
+          <t>893776</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>20,31%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1216908</t>
+          <t>1034609</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1067462</t>
+          <t>981191</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1561188</t>
+          <t>1093105</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1200486</t>
+          <t>1047315</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1062640</t>
+          <t>1002573</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1456666</t>
+          <t>1093269</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2417394</t>
+          <t>2081924</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2193190</t>
+          <t>2015586</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2853389</t>
+          <t>2155108</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>48,98%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2236398</t>
+          <t>2169302</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2236398</t>
+          <t>2169302</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2236398</t>
+          <t>2169302</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4526725</t>
+          <t>4399868</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4526725</t>
+          <t>4399868</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4526725</t>
+          <t>4399868</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>83493</t>
+          <t>95602</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>67859</t>
+          <t>77717</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>103571</t>
+          <t>116581</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>74131</t>
+          <t>85321</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>61319</t>
+          <t>69873</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>88448</t>
+          <t>101570</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>157624</t>
+          <t>180924</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>136292</t>
+          <t>156292</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>180696</t>
+          <t>206373</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>84896</t>
+          <t>94973</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>68264</t>
+          <t>78222</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>104313</t>
+          <t>115745</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>73050</t>
+          <t>87471</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>60185</t>
+          <t>72335</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>89615</t>
+          <t>104748</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>157946</t>
+          <t>182443</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>136923</t>
+          <t>157751</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>183298</t>
+          <t>207795</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>124309</t>
+          <t>138855</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>103271</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>145527</t>
+          <t>162047</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>123779</t>
+          <t>144189</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>108351</t>
+          <t>127876</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>143583</t>
+          <t>165743</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>248088</t>
+          <t>283043</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>222463</t>
+          <t>254239</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>273942</t>
+          <t>315442</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>353761</t>
+          <t>380515</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>325461</t>
+          <t>350455</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>379462</t>
+          <t>408371</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>387796</t>
+          <t>414500</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>365462</t>
+          <t>390271</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>409176</t>
+          <t>437857</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>741557</t>
+          <t>795015</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>708452</t>
+          <t>754258</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>776237</t>
+          <t>829212</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>57,53%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>646459</t>
+          <t>709944</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>646459</t>
+          <t>709944</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>646459</t>
+          <t>709944</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>658756</t>
+          <t>731480</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>658756</t>
+          <t>731480</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>658756</t>
+          <t>731480</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1305215</t>
+          <t>1441425</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1305215</t>
+          <t>1441425</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1305215</t>
+          <t>1441425</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>592007</t>
+          <t>689718</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>466434</t>
+          <t>641368</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>657473</t>
+          <t>741659</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>694977</t>
+          <t>726316</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>590986</t>
+          <t>681364</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>882774</t>
+          <t>772657</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1286984</t>
+          <t>1416034</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1122463</t>
+          <t>1349684</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1449945</t>
+          <t>1489274</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,56%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>438327</t>
+          <t>487372</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>332907</t>
+          <t>443987</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>490598</t>
+          <t>534754</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>464130</t>
+          <t>527785</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>375118</t>
+          <t>487043</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>513508</t>
+          <t>568380</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>902457</t>
+          <t>1015156</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>787075</t>
+          <t>958721</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>979897</t>
+          <t>1074322</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,83%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>627172</t>
+          <t>681546</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>486781</t>
+          <t>628602</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>699091</t>
+          <t>734760</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>612421</t>
+          <t>695413</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>504842</t>
+          <t>653956</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>672589</t>
+          <t>740645</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1239593</t>
+          <t>1376959</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1068726</t>
+          <t>1313337</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1337960</t>
+          <t>1447871</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,99%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1794218</t>
+          <t>1660404</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1651031</t>
+          <t>1595378</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2204417</t>
+          <t>1726285</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1879133</t>
+          <t>1773307</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1734225</t>
+          <t>1718795</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2236738</t>
+          <t>1827309</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3673352</t>
+          <t>3433711</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3449168</t>
+          <t>3345433</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4129734</t>
+          <t>3523190</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>48,65%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3451724</t>
+          <t>3519040</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3451724</t>
+          <t>3519040</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3451724</t>
+          <t>3519040</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3650662</t>
+          <t>3722820</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3650662</t>
+          <t>3722820</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3650662</t>
+          <t>3722820</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7102386</t>
+          <t>7241860</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7102386</t>
+          <t>7241860</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7102386</t>
+          <t>7241860</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
